--- a/hospice_forms/021_hospice_license_application_form--hospice_forms.xlsx
+++ b/hospice_forms/021_hospice_license_application_form--hospice_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>City 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>State 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Zip Code 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>License Date</t>
+          <t>License Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
